--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F043B69-87AA-004F-BF74-BF6930801A43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98395CDD-BB8E-9142-9FF8-D6519929E67D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10840" yWindow="500" windowWidth="16020" windowHeight="16420" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="10840" yWindow="500" windowWidth="16020" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
   <si>
     <t>Genome</t>
   </si>
@@ -154,6 +154,12 @@
   </si>
   <si>
     <t>20230531 - sent by Kiyoto Maekawa</t>
+  </si>
+  <si>
+    <t>Diploptera punctata</t>
+  </si>
+  <si>
+    <t>GCA_030220185.1 - GenBank</t>
   </si>
 </sst>
 </file>
@@ -176,7 +182,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -204,6 +210,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -235,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -246,6 +258,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -580,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -765,29 +784,27 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="2">
-        <v>358</v>
-      </c>
+    <row r="13" spans="1:6" ht="17">
+      <c r="A13" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="10"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="C14" s="2">
-        <v>142</v>
+        <v>358</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -795,13 +812,13 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="5">
-        <v>732</v>
+        <v>35</v>
+      </c>
+      <c r="C15" s="2">
+        <v>142</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -809,10 +826,10 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="5">
         <v>732</v>
@@ -823,13 +840,13 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="2">
-        <v>696</v>
+        <v>12</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="5">
+        <v>732</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -837,27 +854,27 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C18" s="2">
-        <v>616</v>
+        <v>696</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>35</v>
+      <c r="A19" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="C19" s="2">
-        <v>4</v>
+        <v>616</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
@@ -865,13 +882,13 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>34</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="C20" s="2">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -879,13 +896,13 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="C21" s="2">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -893,13 +910,13 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -907,17 +924,31 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="2">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98395CDD-BB8E-9142-9FF8-D6519929E67D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B599E5C-3376-8748-8B47-BBAC26B952B7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10840" yWindow="500" windowWidth="16020" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
@@ -182,7 +182,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -210,12 +210,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -247,7 +241,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -264,7 +258,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -791,7 +784,9 @@
       <c r="B13" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="5">
+        <v>648</v>
+      </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B599E5C-3376-8748-8B47-BBAC26B952B7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8210D034-C050-5C48-B829-59E7FD70383F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10840" yWindow="500" windowWidth="16020" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="16860" yWindow="760" windowWidth="16020" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,13 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="45">
-  <si>
-    <t>Genome</t>
-  </si>
-  <si>
-    <t># of putative HGT inserts</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t xml:space="preserve">Panesthia cribrata </t>
   </si>
@@ -69,18 +63,6 @@
     <t>Periplaneta americana v1</t>
   </si>
   <si>
-    <t>Name/Source</t>
-  </si>
-  <si>
-    <t># of HGT inserts after removing contaminants</t>
-  </si>
-  <si>
-    <t># of HGT inserts after removed false duplicates</t>
-  </si>
-  <si>
-    <t>Avererage length of filtered HGT inserts</t>
-  </si>
-  <si>
     <t>M1</t>
   </si>
   <si>
@@ -138,28 +120,55 @@
     <t>Zootermopsis nevadensis v2</t>
   </si>
   <si>
-    <t>GCA_025594305.2 - GenBank</t>
-  </si>
-  <si>
-    <t>CNA0019281 - CNSA</t>
-  </si>
-  <si>
-    <t>GCA_000762945.2 - GenBank</t>
-  </si>
-  <si>
     <t>Re-assembled PacBio data (sourced from 'PRJNA1098420')</t>
   </si>
   <si>
     <t>Reticulitermes lucifugus</t>
   </si>
   <si>
-    <t>20230531 - sent by Kiyoto Maekawa</t>
-  </si>
-  <si>
     <t>Diploptera punctata</t>
   </si>
   <si>
-    <t>GCA_030220185.1 - GenBank</t>
+    <t>1.v1. HGT insert count</t>
+  </si>
+  <si>
+    <t>1.v2. HGT insert count</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>New</t>
+  </si>
+  <si>
+    <t>GenBank</t>
+  </si>
+  <si>
+    <t>GCA_030220185.1</t>
+  </si>
+  <si>
+    <t>GCA_025594305.2</t>
+  </si>
+  <si>
+    <t>CNA0019281</t>
+  </si>
+  <si>
+    <t>CNSA</t>
+  </si>
+  <si>
+    <t>GCA_000762945.2</t>
+  </si>
+  <si>
+    <t>20230531</t>
+  </si>
+  <si>
+    <t>Sent by Kiyoto Maekawa</t>
+  </si>
+  <si>
+    <t>Species/version</t>
   </si>
 </sst>
 </file>
@@ -592,358 +601,310 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6640625" customWidth="1"/>
-    <col min="3" max="3" width="28.83203125" customWidth="1"/>
-    <col min="4" max="4" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="51.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="B2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1772</v>
+        <v>12</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6">
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="5">
-        <v>3354</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="5"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5454</v>
+        <v>14</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="2">
-        <v>4661</v>
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="2">
-        <v>4115</v>
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="2">
-        <v>3979</v>
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="2">
-        <v>4421</v>
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="5">
-        <v>5090</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>24</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="5"/>
       <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1780</v>
+        <v>0</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="2">
-        <v>3092</v>
+        <v>1</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6">
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="2">
-        <v>4968</v>
+        <v>26</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" ht="17">
+    </row>
+    <row r="13" spans="1:5" ht="17">
       <c r="A13" s="8" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="5">
-        <v>648</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>40</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="5"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6">
+    </row>
+    <row r="14" spans="1:5" ht="17">
       <c r="A14" s="7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="2">
-        <v>358</v>
+        <v>41</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6">
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="2">
-        <v>142</v>
+        <v>7</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6">
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" s="7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="5">
-        <v>732</v>
-      </c>
-      <c r="D16" s="2"/>
+        <v>42</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="5"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6">
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="5">
-        <v>732</v>
-      </c>
-      <c r="D17" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="5"/>
       <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6">
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="2">
-        <v>696</v>
+        <v>21</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6">
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="C19" s="2">
-        <v>616</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6">
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="2">
-        <v>4</v>
+        <v>28</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6">
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="2">
-        <v>89</v>
+        <v>45</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6">
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="2">
-        <v>15</v>
+        <v>3</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6">
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="2">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6">
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="2">
-        <v>8</v>
+        <v>32</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8210D034-C050-5C48-B829-59E7FD70383F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CE6ACF-B61C-194C-BEF5-EEEAE9FF13E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16860" yWindow="760" windowWidth="16020" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="480" yWindow="1780" windowWidth="16020" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
   <si>
     <t xml:space="preserve">Panesthia cribrata </t>
   </si>
@@ -63,18 +63,6 @@
     <t>Periplaneta americana v1</t>
   </si>
   <si>
-    <t>M1</t>
-  </si>
-  <si>
-    <t>Z1</t>
-  </si>
-  <si>
-    <t>Z4</t>
-  </si>
-  <si>
-    <t>Z5</t>
-  </si>
-  <si>
     <t>Panesthia lata</t>
   </si>
   <si>
@@ -93,18 +81,6 @@
     <t>Blattella germanica v1</t>
   </si>
   <si>
-    <t>Z010</t>
-  </si>
-  <si>
-    <t>Z011</t>
-  </si>
-  <si>
-    <t>Z014</t>
-  </si>
-  <si>
-    <t>Z012</t>
-  </si>
-  <si>
     <t>Geoscapheus dilatatus</t>
   </si>
   <si>
@@ -147,28 +123,82 @@
     <t>GenBank</t>
   </si>
   <si>
-    <t>GCA_030220185.1</t>
-  </si>
-  <si>
-    <t>GCA_025594305.2</t>
-  </si>
-  <si>
-    <t>CNA0019281</t>
-  </si>
-  <si>
     <t>CNSA</t>
   </si>
   <si>
-    <t>GCA_000762945.2</t>
-  </si>
-  <si>
-    <t>20230531</t>
-  </si>
-  <si>
     <t>Sent by Kiyoto Maekawa</t>
   </si>
   <si>
     <t>Species/version</t>
+  </si>
+  <si>
+    <t>Znevadensis_20230531.contig</t>
+  </si>
+  <si>
+    <t>Zootermopsis_nevadensis.genome</t>
+  </si>
+  <si>
+    <t>Z4_flye-assembly_polished-it2_filtered</t>
+  </si>
+  <si>
+    <t>Panesthia-cribrata_genome-assembly</t>
+  </si>
+  <si>
+    <t>Reticulitermes_lucifugus.genome</t>
+  </si>
+  <si>
+    <t>Periplaneta_americana.genome</t>
+  </si>
+  <si>
+    <t>Periplaneta-americana_GCA_025594305.2_ASM2559430v2</t>
+  </si>
+  <si>
+    <t>Periplaneta-americana_CNA0019281</t>
+  </si>
+  <si>
+    <t>P-americana_PRJNA1098420_pacbio_prim-assembly</t>
+  </si>
+  <si>
+    <t>Neogeoscapheus-hanni_genome-assembly</t>
+  </si>
+  <si>
+    <t>Geoscapheus-dilatatus_genome-assembly</t>
+  </si>
+  <si>
+    <t>GCA_030220185.1_Dpun_1.1_genomic</t>
+  </si>
+  <si>
+    <t>Cryptotermes_secundus.genome</t>
+  </si>
+  <si>
+    <t>Coptotermes_formosanus.genome</t>
+  </si>
+  <si>
+    <t>Blattella_germanica.genome</t>
+  </si>
+  <si>
+    <t>M1_flye-assembly_run2_polished-it2</t>
+  </si>
+  <si>
+    <t>Z1_flye-assembly_polished-it2_filtered</t>
+  </si>
+  <si>
+    <t>Z5_flye-assembly_polished-it2_filtered</t>
+  </si>
+  <si>
+    <t>Z010_flye_polished_purged_filtered</t>
+  </si>
+  <si>
+    <t>Z011_flye_polished_purged_filtered</t>
+  </si>
+  <si>
+    <t>Z012_flye_polished_purged_filtered</t>
+  </si>
+  <si>
+    <t>Z014_flye_polished_purged_filtered</t>
+  </si>
+  <si>
+    <t>GCA_000762945.2_Bger_2.0_genomic</t>
   </si>
 </sst>
 </file>
@@ -605,50 +635,51 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="51.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.33203125" customWidth="1"/>
+    <col min="3" max="3" width="51.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.83203125" customWidth="1"/>
     <col min="5" max="5" width="41.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="4" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="2"/>
@@ -658,36 +689,36 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -697,10 +728,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -710,23 +741,23 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="2"/>
@@ -735,9 +766,11 @@
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="C10" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -746,33 +779,37 @@
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="5"/>
+      <c r="B11" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="C11" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>45</v>
+      </c>
       <c r="C12" s="5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5" ht="17">
       <c r="A13" s="8" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="2"/>
@@ -785,7 +822,7 @@
         <v>41</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -794,9 +831,11 @@
       <c r="A15" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C15" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -809,7 +848,7 @@
         <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D16" s="5"/>
       <c r="E16" s="2"/>
@@ -818,20 +857,24 @@
       <c r="A17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C17" s="2" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D17" s="5"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
@@ -841,34 +884,36 @@
         <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="5"/>
+        <v>20</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="C20" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -877,9 +922,11 @@
       <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="5"/>
+      <c r="B22" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="C22" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -888,20 +935,24 @@
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="5"/>
+      <c r="B23" s="5" t="s">
+        <v>47</v>
+      </c>
       <c r="C23" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>39</v>
+      </c>
       <c r="C24" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CE6ACF-B61C-194C-BEF5-EEEAE9FF13E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC3DD0A-27B1-3E40-A95D-853EB86FBE01}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="1780" windowWidth="16020" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="15540" yWindow="2720" windowWidth="15740" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
   <si>
     <t xml:space="preserve">Panesthia cribrata </t>
   </si>
@@ -117,9 +117,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>New</t>
-  </si>
-  <si>
     <t>GenBank</t>
   </si>
   <si>
@@ -199,6 +196,63 @@
   </si>
   <si>
     <t>GCA_000762945.2_Bger_2.0_genomic</t>
+  </si>
+  <si>
+    <t>New (this study)</t>
+  </si>
+  <si>
+    <t>2.v1. HGT insert count</t>
+  </si>
+  <si>
+    <t>2.v2. HGT insert count</t>
+  </si>
+  <si>
+    <t>3.v1. HGT insert count</t>
+  </si>
+  <si>
+    <t>3.v2. HGT insert count</t>
+  </si>
+  <si>
+    <t>4.v1. HGT insert count</t>
+  </si>
+  <si>
+    <t>4.v2. HGT insert count</t>
+  </si>
+  <si>
+    <t>5.v1. HGT insert count</t>
+  </si>
+  <si>
+    <t>5.v2. HGT insert count</t>
+  </si>
+  <si>
+    <t>5.v3. HGT insert count</t>
+  </si>
+  <si>
+    <t>6.v1. HGT insert count</t>
+  </si>
+  <si>
+    <t>6.v2. HGT insert count</t>
+  </si>
+  <si>
+    <t>6.v3. HGT insert count</t>
+  </si>
+  <si>
+    <t>6.v4. HGT insert count</t>
+  </si>
+  <si>
+    <t>6.v5. HGT insert count</t>
+  </si>
+  <si>
+    <t>6.v6. HGT insert count</t>
+  </si>
+  <si>
+    <t>7.v1. HGT insert count</t>
+  </si>
+  <si>
+    <t>7.v2. HGT insert count</t>
+  </si>
+  <si>
+    <t>7.v3. HGT insert count</t>
   </si>
 </sst>
 </file>
@@ -631,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -639,11 +693,14 @@
     <col min="3" max="3" width="51.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.83203125" customWidth="1"/>
     <col min="5" max="5" width="41.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="13" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.5" customWidth="1"/>
+    <col min="15" max="23" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:23">
       <c r="A1" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>29</v>
@@ -657,305 +714,865 @@
       <c r="E1" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1784</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2168</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="D3" s="5">
+        <v>3377</v>
+      </c>
+      <c r="E3" s="2">
+        <v>4005</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="D4" s="2">
+        <v>5483</v>
+      </c>
+      <c r="E4" s="2">
+        <v>6593</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4692</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5530</v>
+      </c>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4148</v>
+      </c>
+      <c r="E6" s="2">
+        <v>4937</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4002</v>
+      </c>
+      <c r="E7" s="2">
+        <v>4738</v>
+      </c>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4440</v>
+      </c>
+      <c r="E8" s="2">
+        <v>5207</v>
+      </c>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10" spans="1:5">
+        <v>57</v>
+      </c>
+      <c r="D9" s="5">
+        <v>5113</v>
+      </c>
+      <c r="E9" s="2">
+        <v>6102</v>
+      </c>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="D10" s="2">
+        <v>1793</v>
+      </c>
+      <c r="E10" s="2">
+        <v>2178</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="D11" s="2">
+        <v>3105</v>
+      </c>
+      <c r="E11" s="2">
+        <v>3575</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" ht="17">
+      <c r="D12" s="2">
+        <v>4979</v>
+      </c>
+      <c r="E12" s="2">
+        <v>5698</v>
+      </c>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+    </row>
+    <row r="13" spans="1:23" ht="17">
       <c r="A13" s="8" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" ht="17">
+        <v>30</v>
+      </c>
+      <c r="D13" s="5">
+        <v>663</v>
+      </c>
+      <c r="E13" s="2">
+        <v>1358</v>
+      </c>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+    </row>
+    <row r="14" spans="1:23" ht="17">
       <c r="A14" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:5">
+        <v>30</v>
+      </c>
+      <c r="D14" s="2">
+        <v>361</v>
+      </c>
+      <c r="E14" s="2">
+        <v>736</v>
+      </c>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="D15" s="2">
+        <v>149</v>
+      </c>
+      <c r="E15" s="2">
+        <v>426</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" s="7" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="1:5">
+        <v>31</v>
+      </c>
+      <c r="D16" s="5">
+        <v>733</v>
+      </c>
+      <c r="E16" s="2">
+        <v>1032</v>
+      </c>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="7" t="s">
         <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="D17" s="5">
+        <v>735</v>
+      </c>
+      <c r="E17" s="2">
+        <v>1053</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="D18" s="2">
+        <v>712</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1316</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="1:5">
+        <v>30</v>
+      </c>
+      <c r="D19" s="2">
+        <v>628</v>
+      </c>
+      <c r="E19" s="2">
+        <v>1223</v>
+      </c>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="D20" s="2">
+        <v>4</v>
+      </c>
+      <c r="E20" s="2">
+        <v>30</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" spans="1:5">
+        <v>32</v>
+      </c>
+      <c r="D21" s="2">
+        <v>97</v>
+      </c>
+      <c r="E21" s="2">
+        <v>198</v>
+      </c>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="D22" s="2">
+        <v>16</v>
+      </c>
+      <c r="E22" s="2">
+        <v>63</v>
+      </c>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="D23" s="2">
+        <v>5</v>
+      </c>
+      <c r="E23" s="2">
+        <v>47</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+    </row>
+    <row r="24" spans="1:23">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="D24" s="2">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2">
+        <v>47</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kewart/Documents/GitHub/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC3DD0A-27B1-3E40-A95D-853EB86FBE01}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CB8599-DF04-4D40-9B09-54B575ACF215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15540" yWindow="2720" windowWidth="15740" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="11020" yWindow="6420" windowWidth="29800" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -259,7 +259,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -334,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -342,13 +342,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -686,7 +685,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
   <dimension ref="A1:W24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.33203125" customWidth="1"/>
@@ -698,7 +697,7 @@
     <col min="15" max="23" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -769,14 +768,14 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D2" s="2">
@@ -789,8 +788,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="J2" s="2">
+        <v>1603</v>
+      </c>
+      <c r="K2" s="2">
+        <v>1742</v>
+      </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -804,17 +807,17 @@
       <c r="V2" s="2"/>
       <c r="W2" s="2"/>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="2">
         <v>3377</v>
       </c>
       <c r="E3" s="2">
@@ -824,8 +827,12 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
+      <c r="J3" s="2">
+        <v>2895</v>
+      </c>
+      <c r="K3" s="2">
+        <v>3111</v>
+      </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -839,14 +846,14 @@
       <c r="V3" s="2"/>
       <c r="W3" s="2"/>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D4" s="2">
@@ -859,8 +866,12 @@
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
+      <c r="J4" s="2">
+        <v>5002</v>
+      </c>
+      <c r="K4" s="2">
+        <v>5356</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -874,14 +885,14 @@
       <c r="V4" s="2"/>
       <c r="W4" s="2"/>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D5" s="2">
@@ -894,8 +905,12 @@
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+      <c r="J5" s="2">
+        <v>4193</v>
+      </c>
+      <c r="K5" s="2">
+        <v>4387</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
@@ -909,14 +924,14 @@
       <c r="V5" s="2"/>
       <c r="W5" s="2"/>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="2">
@@ -929,8 +944,12 @@
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+      <c r="J6" s="2">
+        <v>3852</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3958</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
@@ -944,14 +963,14 @@
       <c r="V6" s="2"/>
       <c r="W6" s="2"/>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D7" s="2">
@@ -964,8 +983,12 @@
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="J7" s="2">
+        <v>3700</v>
+      </c>
+      <c r="K7" s="2">
+        <v>3832</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
@@ -979,14 +1002,14 @@
       <c r="V7" s="2"/>
       <c r="W7" s="2"/>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="2">
@@ -999,8 +1022,12 @@
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="J8" s="2">
+        <v>3987</v>
+      </c>
+      <c r="K8" s="2">
+        <v>4233</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -1014,17 +1041,17 @@
       <c r="V8" s="2"/>
       <c r="W8" s="2"/>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="2">
         <v>5113</v>
       </c>
       <c r="E9" s="2">
@@ -1034,8 +1061,12 @@
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="J9" s="2">
+        <v>4646</v>
+      </c>
+      <c r="K9" s="2">
+        <v>5041</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -1049,14 +1080,14 @@
       <c r="V9" s="2"/>
       <c r="W9" s="2"/>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D10" s="2">
@@ -1069,8 +1100,12 @@
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="J10" s="2">
+        <v>1534</v>
+      </c>
+      <c r="K10" s="2">
+        <v>1708</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -1084,14 +1119,14 @@
       <c r="V10" s="2"/>
       <c r="W10" s="2"/>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="2">
@@ -1104,8 +1139,12 @@
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="J11" s="2">
+        <v>2769</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2989</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -1119,14 +1158,14 @@
       <c r="V11" s="2"/>
       <c r="W11" s="2"/>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="2">
@@ -1139,8 +1178,12 @@
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="J12" s="2">
+        <v>4329</v>
+      </c>
+      <c r="K12" s="2">
+        <v>4597</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -1154,17 +1197,17 @@
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
     </row>
-    <row r="13" spans="1:23" ht="17">
-      <c r="A13" s="8" t="s">
+    <row r="13" spans="1:23" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="2">
         <v>663</v>
       </c>
       <c r="E13" s="2">
@@ -1174,8 +1217,12 @@
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="J13" s="2">
+        <v>551</v>
+      </c>
+      <c r="K13" s="2">
+        <v>938</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -1189,14 +1236,14 @@
       <c r="V13" s="2"/>
       <c r="W13" s="2"/>
     </row>
-    <row r="14" spans="1:23" ht="17">
-      <c r="A14" s="7" t="s">
+    <row r="14" spans="1:23" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>30</v>
       </c>
       <c r="D14" s="2">
@@ -1209,8 +1256,12 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="J14" s="2">
+        <v>289</v>
+      </c>
+      <c r="K14" s="2">
+        <v>408</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -1224,8 +1275,8 @@
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
     </row>
-    <row r="15" spans="1:23">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1244,8 +1295,12 @@
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="J15" s="2">
+        <v>111</v>
+      </c>
+      <c r="K15" s="2">
+        <v>240</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -1259,8 +1314,8 @@
       <c r="V15" s="2"/>
       <c r="W15" s="2"/>
     </row>
-    <row r="16" spans="1:23">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1269,7 +1324,7 @@
       <c r="C16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="2">
         <v>733</v>
       </c>
       <c r="E16" s="2">
@@ -1279,8 +1334,12 @@
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="J16" s="2">
+        <v>652</v>
+      </c>
+      <c r="K16" s="2">
+        <v>791</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -1294,8 +1353,8 @@
       <c r="V16" s="2"/>
       <c r="W16" s="2"/>
     </row>
-    <row r="17" spans="1:23">
-      <c r="A17" s="7" t="s">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1304,7 +1363,7 @@
       <c r="C17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="2">
         <v>735</v>
       </c>
       <c r="E17" s="2">
@@ -1314,8 +1373,12 @@
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="J17" s="2">
+        <v>652</v>
+      </c>
+      <c r="K17" s="2">
+        <v>760</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1329,14 +1392,14 @@
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
     </row>
-    <row r="18" spans="1:23">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="2">
@@ -1349,8 +1412,12 @@
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
+      <c r="J18" s="2">
+        <v>572</v>
+      </c>
+      <c r="K18" s="2">
+        <v>886</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
@@ -1364,8 +1431,8 @@
       <c r="V18" s="2"/>
       <c r="W18" s="2"/>
     </row>
-    <row r="19" spans="1:23">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1384,8 +1451,12 @@
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
+      <c r="J19" s="2">
+        <v>526</v>
+      </c>
+      <c r="K19" s="2">
+        <v>825</v>
+      </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
@@ -1399,14 +1470,14 @@
       <c r="V19" s="2"/>
       <c r="W19" s="2"/>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="2">
@@ -1419,8 +1490,12 @@
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
+      <c r="J20" s="2">
+        <v>1</v>
+      </c>
+      <c r="K20" s="2">
+        <v>3</v>
+      </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -1434,14 +1509,14 @@
       <c r="V20" s="2"/>
       <c r="W20" s="2"/>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>32</v>
       </c>
       <c r="D21" s="2">
@@ -1454,8 +1529,12 @@
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+      <c r="J21" s="2">
+        <v>66</v>
+      </c>
+      <c r="K21" s="2">
+        <v>113</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
@@ -1469,14 +1548,14 @@
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="2">
@@ -1489,8 +1568,12 @@
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>8</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -1504,14 +1587,14 @@
       <c r="V22" s="2"/>
       <c r="W22" s="2"/>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="2">
@@ -1524,8 +1607,12 @@
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2">
+        <v>11</v>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -1539,14 +1626,14 @@
       <c r="V23" s="2"/>
       <c r="W23" s="2"/>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="2">
@@ -1559,8 +1646,12 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
+      <c r="J24" s="2">
+        <v>8</v>
+      </c>
+      <c r="K24" s="2">
+        <v>47</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kewart/Documents/GitHub/HGT_pipeline/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CB8599-DF04-4D40-9B09-54B575ACF215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3F3DE1-0E85-514B-B337-73CB33D6B67D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11020" yWindow="6420" windowWidth="29800" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="4440" yWindow="4520" windowWidth="17520" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
   <si>
     <t xml:space="preserve">Panesthia cribrata </t>
   </si>
@@ -225,27 +225,12 @@
     <t>5.v2. HGT insert count</t>
   </si>
   <si>
-    <t>5.v3. HGT insert count</t>
-  </si>
-  <si>
     <t>6.v1. HGT insert count</t>
   </si>
   <si>
     <t>6.v2. HGT insert count</t>
   </si>
   <si>
-    <t>6.v3. HGT insert count</t>
-  </si>
-  <si>
-    <t>6.v4. HGT insert count</t>
-  </si>
-  <si>
-    <t>6.v5. HGT insert count</t>
-  </si>
-  <si>
-    <t>6.v6. HGT insert count</t>
-  </si>
-  <si>
     <t>7.v1. HGT insert count</t>
   </si>
   <si>
@@ -253,13 +238,22 @@
   </si>
   <si>
     <t>7.v3. HGT insert count</t>
+  </si>
+  <si>
+    <t>7.v4. HGT insert count</t>
+  </si>
+  <si>
+    <t>8.v1. HGT insert count</t>
+  </si>
+  <si>
+    <t>8.v2. HGT insert count</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -275,7 +269,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -303,6 +297,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -334,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -350,11 +350,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -684,20 +697,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
-  <dimension ref="A1:W24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U49"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.33203125" customWidth="1"/>
     <col min="3" max="3" width="51.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.83203125" customWidth="1"/>
     <col min="5" max="5" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="13" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.5" customWidth="1"/>
-    <col min="15" max="23" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="21" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -761,14 +772,8 @@
       <c r="U1" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="V1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -794,8 +799,12 @@
       <c r="K2" s="2">
         <v>1742</v>
       </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="L2" s="2">
+        <v>1573</v>
+      </c>
+      <c r="M2" s="2">
+        <v>1717</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -804,10 +813,8 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -833,8 +840,12 @@
       <c r="K3" s="2">
         <v>3111</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="L3" s="2">
+        <v>2843</v>
+      </c>
+      <c r="M3" s="2">
+        <v>3061</v>
+      </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -843,10 +854,8 @@
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -872,8 +881,12 @@
       <c r="K4" s="2">
         <v>5356</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="L4" s="2">
+        <v>4913</v>
+      </c>
+      <c r="M4" s="2">
+        <v>5284</v>
+      </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
@@ -882,10 +895,8 @@
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -911,8 +922,12 @@
       <c r="K5" s="2">
         <v>4387</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
+      <c r="L5" s="2">
+        <v>4117</v>
+      </c>
+      <c r="M5" s="2">
+        <v>4327</v>
+      </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
@@ -921,10 +936,8 @@
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -950,8 +963,12 @@
       <c r="K6" s="2">
         <v>3958</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
+      <c r="L6" s="2">
+        <v>3766</v>
+      </c>
+      <c r="M6" s="2">
+        <v>3874</v>
+      </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2"/>
@@ -960,10 +977,8 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:21">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -989,8 +1004,12 @@
       <c r="K7" s="2">
         <v>3832</v>
       </c>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
+      <c r="L7" s="2">
+        <v>3636</v>
+      </c>
+      <c r="M7" s="2">
+        <v>3771</v>
+      </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -999,10 +1018,8 @@
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1028,8 +1045,12 @@
       <c r="K8" s="2">
         <v>4233</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
+      <c r="L8" s="2">
+        <v>3926</v>
+      </c>
+      <c r="M8" s="2">
+        <v>4174</v>
+      </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2"/>
@@ -1038,10 +1059,8 @@
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:21">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1067,8 +1086,12 @@
       <c r="K9" s="2">
         <v>5041</v>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
+      <c r="L9" s="2">
+        <v>4561</v>
+      </c>
+      <c r="M9" s="2">
+        <v>4962</v>
+      </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" s="2"/>
@@ -1077,10 +1100,8 @@
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1106,8 +1127,12 @@
       <c r="K10" s="2">
         <v>1708</v>
       </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
+      <c r="L10" s="2">
+        <v>1498</v>
+      </c>
+      <c r="M10" s="2">
+        <v>1670</v>
+      </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" s="2"/>
@@ -1116,10 +1141,8 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:21">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1145,8 +1168,12 @@
       <c r="K11" s="2">
         <v>2989</v>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
+      <c r="L11" s="2">
+        <v>2723</v>
+      </c>
+      <c r="M11" s="2">
+        <v>2948</v>
+      </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" s="2"/>
@@ -1155,10 +1182,8 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1184,8 +1209,12 @@
       <c r="K12" s="2">
         <v>4597</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
+      <c r="L12" s="2">
+        <v>4252</v>
+      </c>
+      <c r="M12" s="2">
+        <v>4525</v>
+      </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
@@ -1194,10 +1223,8 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:21" ht="17">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -1223,8 +1250,12 @@
       <c r="K13" s="2">
         <v>938</v>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
+      <c r="L13" s="2">
+        <v>525</v>
+      </c>
+      <c r="M13" s="2">
+        <v>896</v>
+      </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" s="2"/>
@@ -1233,10 +1264,8 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" ht="17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:21" ht="17">
       <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
@@ -1262,8 +1291,12 @@
       <c r="K14" s="2">
         <v>408</v>
       </c>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="L14" s="2">
+        <v>288</v>
+      </c>
+      <c r="M14" s="2">
+        <v>406</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" s="2"/>
@@ -1272,10 +1305,8 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
@@ -1301,8 +1332,12 @@
       <c r="K15" s="2">
         <v>240</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="L15" s="2">
+        <v>94</v>
+      </c>
+      <c r="M15" s="2">
+        <v>221</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" s="2"/>
@@ -1311,10 +1346,8 @@
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
@@ -1340,8 +1373,12 @@
       <c r="K16" s="2">
         <v>791</v>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+      <c r="L16" s="2">
+        <v>648</v>
+      </c>
+      <c r="M16" s="2">
+        <v>787</v>
+      </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" s="2"/>
@@ -1350,10 +1387,8 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
@@ -1379,8 +1414,12 @@
       <c r="K17" s="2">
         <v>760</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+      <c r="L17" s="2">
+        <v>639</v>
+      </c>
+      <c r="M17" s="2">
+        <v>738</v>
+      </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
@@ -1389,10 +1428,8 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:21">
       <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
@@ -1418,8 +1455,12 @@
       <c r="K18" s="2">
         <v>886</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="L18" s="2">
+        <v>301</v>
+      </c>
+      <c r="M18" s="2">
+        <v>542</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" s="2"/>
@@ -1428,10 +1469,8 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:21">
       <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
@@ -1457,8 +1496,12 @@
       <c r="K19" s="2">
         <v>825</v>
       </c>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
+      <c r="L19" s="2">
+        <v>279</v>
+      </c>
+      <c r="M19" s="2">
+        <v>507</v>
+      </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
@@ -1467,10 +1510,8 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:21">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
@@ -1496,8 +1537,12 @@
       <c r="K20" s="2">
         <v>3</v>
       </c>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
+        <v>2</v>
+      </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2"/>
@@ -1506,10 +1551,8 @@
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:21">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
@@ -1535,8 +1578,12 @@
       <c r="K21" s="2">
         <v>113</v>
       </c>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
+      <c r="L21" s="2">
+        <v>12</v>
+      </c>
+      <c r="M21" s="2">
+        <v>36</v>
+      </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
@@ -1545,10 +1592,8 @@
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:21">
       <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1574,8 +1619,12 @@
       <c r="K22" s="2">
         <v>8</v>
       </c>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>6</v>
+      </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" s="2"/>
@@ -1584,10 +1633,8 @@
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:21">
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
@@ -1613,8 +1660,12 @@
       <c r="K23" s="2">
         <v>11</v>
       </c>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>9</v>
+      </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
@@ -1623,10 +1674,8 @@
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:21">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
@@ -1652,8 +1701,12 @@
       <c r="K24" s="2">
         <v>47</v>
       </c>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
+      <c r="L24" s="10">
+        <v>8</v>
+      </c>
+      <c r="M24" s="2">
+        <v>46</v>
+      </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" s="2"/>
@@ -1662,8 +1715,188 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28">
+        <v>3061</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29">
+        <v>5284</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30">
+        <v>4327</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31">
+        <v>3874</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32">
+        <v>3771</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33">
+        <v>4174</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34">
+        <v>4962</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>0</v>
+      </c>
+      <c r="B35">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>1</v>
+      </c>
+      <c r="B36">
+        <v>2948</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B37">
+        <v>4525</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>25</v>
+      </c>
+      <c r="B38">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>24</v>
+      </c>
+      <c r="B49" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A3F3DE1-0E85-514B-B337-73CB33D6B67D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CBDBC3-1CFD-AC40-B2BF-3F6AA87D9D6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="4520" windowWidth="17520" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="9780" yWindow="880" windowWidth="22260" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
   <si>
     <t xml:space="preserve">Panesthia cribrata </t>
   </si>
@@ -269,7 +269,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,12 +297,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -350,24 +344,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -697,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
-  <dimension ref="A1:U49"/>
+  <dimension ref="A1:U51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -783,30 +766,26 @@
       <c r="C2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="2">
-        <v>1784</v>
-      </c>
-      <c r="E2" s="2">
-        <v>2168</v>
-      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="2">
-        <v>1603</v>
-      </c>
-      <c r="K2" s="2">
-        <v>1742</v>
-      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
       <c r="L2" s="2">
-        <v>1573</v>
+        <v>1618</v>
       </c>
       <c r="M2" s="2">
-        <v>1717</v>
-      </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+        <v>1877</v>
+      </c>
+      <c r="N2" s="2">
+        <v>1588</v>
+      </c>
+      <c r="O2" s="2">
+        <v>1849</v>
+      </c>
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
@@ -824,30 +803,26 @@
       <c r="C3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="2">
-        <v>3377</v>
-      </c>
-      <c r="E3" s="2">
-        <v>4005</v>
-      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
-      <c r="J3" s="2">
-        <v>2895</v>
-      </c>
-      <c r="K3" s="2">
-        <v>3111</v>
-      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
       <c r="L3" s="2">
-        <v>2843</v>
+        <v>2974</v>
       </c>
       <c r="M3" s="2">
-        <v>3061</v>
-      </c>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+        <v>3471</v>
+      </c>
+      <c r="N3" s="2">
+        <v>2920</v>
+      </c>
+      <c r="O3" s="2">
+        <v>3414</v>
+      </c>
       <c r="P3" s="2"/>
       <c r="Q3" s="2"/>
       <c r="R3" s="2"/>
@@ -865,30 +840,26 @@
       <c r="C4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D4" s="2">
-        <v>5483</v>
-      </c>
-      <c r="E4" s="2">
-        <v>6593</v>
-      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="2">
-        <v>5002</v>
-      </c>
-      <c r="K4" s="2">
-        <v>5356</v>
-      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
       <c r="L4" s="2">
-        <v>4913</v>
+        <v>5045</v>
       </c>
       <c r="M4" s="2">
-        <v>5284</v>
-      </c>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
+        <v>5923</v>
+      </c>
+      <c r="N4" s="2">
+        <v>4955</v>
+      </c>
+      <c r="O4" s="2">
+        <v>5841</v>
+      </c>
       <c r="P4" s="2"/>
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
@@ -906,30 +877,26 @@
       <c r="C5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="2">
-        <v>4692</v>
-      </c>
-      <c r="E5" s="2">
-        <v>5530</v>
-      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="2">
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2">
+        <v>4271</v>
+      </c>
+      <c r="M5" s="2">
+        <v>4933</v>
+      </c>
+      <c r="N5" s="2">
         <v>4193</v>
       </c>
-      <c r="K5" s="2">
-        <v>4387</v>
-      </c>
-      <c r="L5" s="2">
-        <v>4117</v>
-      </c>
-      <c r="M5" s="2">
-        <v>4327</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+      <c r="O5" s="2">
+        <v>4865</v>
+      </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
@@ -947,30 +914,26 @@
       <c r="C6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="2">
-        <v>4148</v>
-      </c>
-      <c r="E6" s="2">
-        <v>4937</v>
-      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
-      <c r="J6" s="2">
-        <v>3852</v>
-      </c>
-      <c r="K6" s="2">
-        <v>3958</v>
-      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
       <c r="L6" s="2">
-        <v>3766</v>
+        <v>3880</v>
       </c>
       <c r="M6" s="2">
-        <v>3874</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
+        <v>4471</v>
+      </c>
+      <c r="N6" s="2">
+        <v>3794</v>
+      </c>
+      <c r="O6" s="2">
+        <v>4378</v>
+      </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
@@ -988,30 +951,26 @@
       <c r="C7" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D7" s="2">
-        <v>4002</v>
-      </c>
-      <c r="E7" s="2">
-        <v>4738</v>
-      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
-      <c r="J7" s="2">
-        <v>3700</v>
-      </c>
-      <c r="K7" s="2">
-        <v>3832</v>
-      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
       <c r="L7" s="2">
-        <v>3636</v>
+        <v>3737</v>
       </c>
       <c r="M7" s="2">
-        <v>3771</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+        <v>4315</v>
+      </c>
+      <c r="N7" s="2">
+        <v>3673</v>
+      </c>
+      <c r="O7" s="2">
+        <v>4248</v>
+      </c>
       <c r="P7" s="2"/>
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
@@ -1029,30 +988,26 @@
       <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="2">
-        <v>4440</v>
-      </c>
-      <c r="E8" s="2">
-        <v>5207</v>
-      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
-      <c r="J8" s="2">
-        <v>3987</v>
-      </c>
-      <c r="K8" s="2">
-        <v>4233</v>
-      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
       <c r="L8" s="2">
-        <v>3926</v>
+        <v>4095</v>
       </c>
       <c r="M8" s="2">
-        <v>4174</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+        <v>4690</v>
+      </c>
+      <c r="N8" s="2">
+        <v>4031</v>
+      </c>
+      <c r="O8" s="2">
+        <v>4621</v>
+      </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
@@ -1070,30 +1025,26 @@
       <c r="C9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="2">
-        <v>5113</v>
-      </c>
-      <c r="E9" s="2">
-        <v>6102</v>
-      </c>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="2">
-        <v>4646</v>
-      </c>
-      <c r="K9" s="2">
-        <v>5041</v>
-      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
       <c r="L9" s="2">
-        <v>4561</v>
+        <v>4705</v>
       </c>
       <c r="M9" s="2">
-        <v>4962</v>
-      </c>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+        <v>5472</v>
+      </c>
+      <c r="N9" s="2">
+        <v>4619</v>
+      </c>
+      <c r="O9" s="2">
+        <v>5389</v>
+      </c>
       <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -1111,30 +1062,26 @@
       <c r="C10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="2">
-        <v>1793</v>
-      </c>
-      <c r="E10" s="2">
-        <v>2178</v>
-      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
-      <c r="J10" s="2">
-        <v>1534</v>
-      </c>
-      <c r="K10" s="2">
-        <v>1708</v>
-      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
       <c r="L10" s="2">
-        <v>1498</v>
+        <v>1572</v>
       </c>
       <c r="M10" s="2">
-        <v>1670</v>
-      </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+        <v>1856</v>
+      </c>
+      <c r="N10" s="2">
+        <v>1532</v>
+      </c>
+      <c r="O10" s="2">
+        <v>1814</v>
+      </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -1152,30 +1099,26 @@
       <c r="C11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="2">
-        <v>3105</v>
-      </c>
-      <c r="E11" s="2">
-        <v>3575</v>
-      </c>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
-      <c r="J11" s="2">
-        <v>2769</v>
-      </c>
-      <c r="K11" s="2">
-        <v>2989</v>
-      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
       <c r="L11" s="2">
-        <v>2723</v>
+        <v>2798</v>
       </c>
       <c r="M11" s="2">
-        <v>2948</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+        <v>3163</v>
+      </c>
+      <c r="N11" s="2">
+        <v>2751</v>
+      </c>
+      <c r="O11" s="2">
+        <v>3120</v>
+      </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -1193,30 +1136,26 @@
       <c r="C12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="2">
-        <v>4979</v>
-      </c>
-      <c r="E12" s="2">
-        <v>5698</v>
-      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
-      <c r="J12" s="2">
-        <v>4329</v>
-      </c>
-      <c r="K12" s="2">
-        <v>4597</v>
-      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
       <c r="L12" s="2">
-        <v>4252</v>
+        <v>4334</v>
       </c>
       <c r="M12" s="2">
-        <v>4525</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+        <v>4903</v>
+      </c>
+      <c r="N12" s="2">
+        <v>4257</v>
+      </c>
+      <c r="O12" s="2">
+        <v>4822</v>
+      </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -1234,30 +1173,26 @@
       <c r="C13" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D13" s="2">
-        <v>663</v>
-      </c>
-      <c r="E13" s="2">
-        <v>1358</v>
-      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
-      <c r="J13" s="2">
-        <v>551</v>
-      </c>
-      <c r="K13" s="2">
-        <v>938</v>
-      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
       <c r="L13" s="2">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="M13" s="2">
-        <v>896</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+        <v>914</v>
+      </c>
+      <c r="N13" s="2">
+        <v>511</v>
+      </c>
+      <c r="O13" s="2">
+        <v>875</v>
+      </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -1275,30 +1210,26 @@
       <c r="C14" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="2">
-        <v>361</v>
-      </c>
-      <c r="E14" s="2">
-        <v>736</v>
-      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="2">
-        <v>289</v>
-      </c>
-      <c r="K14" s="2">
-        <v>408</v>
-      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
       <c r="L14" s="2">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="M14" s="2">
-        <v>406</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+        <v>468</v>
+      </c>
+      <c r="N14" s="2">
+        <v>308</v>
+      </c>
+      <c r="O14" s="2">
+        <v>466</v>
+      </c>
       <c r="P14" s="2"/>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -1316,30 +1247,26 @@
       <c r="C15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="2">
-        <v>149</v>
-      </c>
-      <c r="E15" s="2">
-        <v>426</v>
-      </c>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
-      <c r="J15" s="2">
-        <v>111</v>
-      </c>
-      <c r="K15" s="2">
-        <v>240</v>
-      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
       <c r="L15" s="2">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="M15" s="2">
-        <v>221</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N15" s="2">
+        <v>101</v>
+      </c>
+      <c r="O15" s="2">
+        <v>246</v>
+      </c>
       <c r="P15" s="2"/>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -1357,30 +1284,26 @@
       <c r="C16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="2">
-        <v>733</v>
-      </c>
-      <c r="E16" s="2">
-        <v>1032</v>
-      </c>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
-      <c r="J16" s="2">
-        <v>652</v>
-      </c>
-      <c r="K16" s="2">
-        <v>791</v>
-      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
       <c r="L16" s="2">
-        <v>648</v>
+        <v>661</v>
       </c>
       <c r="M16" s="2">
-        <v>787</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+        <v>845</v>
+      </c>
+      <c r="N16" s="2">
+        <v>658</v>
+      </c>
+      <c r="O16" s="2">
+        <v>840</v>
+      </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -1398,30 +1321,26 @@
       <c r="C17" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="2">
-        <v>735</v>
-      </c>
-      <c r="E17" s="2">
-        <v>1053</v>
-      </c>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
-      <c r="J17" s="2">
-        <v>652</v>
-      </c>
-      <c r="K17" s="2">
-        <v>760</v>
-      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
       <c r="L17" s="2">
-        <v>639</v>
+        <v>661</v>
       </c>
       <c r="M17" s="2">
-        <v>738</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+        <v>824</v>
+      </c>
+      <c r="N17" s="2">
+        <v>648</v>
+      </c>
+      <c r="O17" s="2">
+        <v>794</v>
+      </c>
       <c r="P17" s="2"/>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -1439,30 +1358,26 @@
       <c r="C18" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="2">
-        <v>712</v>
-      </c>
-      <c r="E18" s="2">
-        <v>1316</v>
-      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
-      <c r="J18" s="2">
-        <v>572</v>
-      </c>
-      <c r="K18" s="2">
-        <v>886</v>
-      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
       <c r="L18" s="2">
-        <v>301</v>
+        <v>557</v>
       </c>
       <c r="M18" s="2">
-        <v>542</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+        <v>943</v>
+      </c>
+      <c r="N18" s="2">
+        <v>278</v>
+      </c>
+      <c r="O18" s="2">
+        <v>543</v>
+      </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
@@ -1480,30 +1395,26 @@
       <c r="C19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D19" s="2">
-        <v>628</v>
-      </c>
-      <c r="E19" s="2">
-        <v>1223</v>
-      </c>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
-      <c r="J19" s="2">
-        <v>526</v>
-      </c>
-      <c r="K19" s="2">
-        <v>825</v>
-      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
       <c r="L19" s="2">
-        <v>279</v>
+        <v>558</v>
       </c>
       <c r="M19" s="2">
-        <v>507</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+        <v>952</v>
+      </c>
+      <c r="N19" s="2">
+        <v>285</v>
+      </c>
+      <c r="O19" s="2">
+        <v>555</v>
+      </c>
       <c r="P19" s="2"/>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -1521,30 +1432,26 @@
       <c r="C20" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="2">
-        <v>4</v>
-      </c>
-      <c r="E20" s="2">
-        <v>30</v>
-      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
-      <c r="J20" s="2">
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2">
         <v>1</v>
       </c>
-      <c r="K20" s="2">
+      <c r="M20" s="2">
         <v>3</v>
       </c>
-      <c r="L20" s="2">
+      <c r="N20" s="2">
         <v>0</v>
       </c>
-      <c r="M20" s="2">
+      <c r="O20" s="2">
         <v>2</v>
       </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
       <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
@@ -1562,30 +1469,26 @@
       <c r="C21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="2">
-        <v>97</v>
-      </c>
-      <c r="E21" s="2">
-        <v>198</v>
-      </c>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
-      <c r="J21" s="2">
-        <v>66</v>
-      </c>
-      <c r="K21" s="2">
-        <v>113</v>
-      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
       <c r="L21" s="2">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="M21" s="2">
-        <v>36</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N21" s="2">
+        <v>14</v>
+      </c>
+      <c r="O21" s="2">
+        <v>50</v>
+      </c>
       <c r="P21" s="2"/>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
@@ -1603,30 +1506,26 @@
       <c r="C22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="2">
-        <v>16</v>
-      </c>
-      <c r="E22" s="2">
-        <v>63</v>
-      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
-      <c r="J22" s="2">
-        <v>0</v>
-      </c>
-      <c r="K22" s="2">
-        <v>8</v>
-      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
       <c r="L22" s="2">
         <v>0</v>
       </c>
       <c r="M22" s="2">
+        <v>10</v>
+      </c>
+      <c r="N22" s="2">
+        <v>0</v>
+      </c>
+      <c r="O22" s="2">
         <v>6</v>
       </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
       <c r="P22" s="2"/>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
@@ -1644,30 +1543,26 @@
       <c r="C23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="2">
-        <v>5</v>
-      </c>
-      <c r="E23" s="2">
-        <v>47</v>
-      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
-      <c r="J23" s="2">
-        <v>0</v>
-      </c>
-      <c r="K23" s="2">
-        <v>11</v>
-      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
       <c r="L23" s="2">
         <v>0</v>
       </c>
       <c r="M23" s="2">
+        <v>11</v>
+      </c>
+      <c r="N23" s="2">
+        <v>0</v>
+      </c>
+      <c r="O23" s="2">
         <v>9</v>
       </c>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
       <c r="P23" s="2"/>
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
@@ -1685,30 +1580,26 @@
       <c r="C24" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="2">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2">
-        <v>47</v>
-      </c>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="2">
-        <v>8</v>
-      </c>
-      <c r="K24" s="2">
-        <v>47</v>
-      </c>
-      <c r="L24" s="10">
-        <v>8</v>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="9">
+        <v>7</v>
       </c>
       <c r="M24" s="2">
         <v>46</v>
       </c>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="N24" s="9">
+        <v>7</v>
+      </c>
+      <c r="O24" s="2">
+        <v>46</v>
+      </c>
       <c r="P24" s="2"/>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
@@ -1717,186 +1608,104 @@
       <c r="U24" s="2"/>
     </row>
     <row r="27" spans="1:21">
-      <c r="A27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27">
-        <v>1717</v>
-      </c>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
     </row>
     <row r="28" spans="1:21">
-      <c r="A28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28">
-        <v>3061</v>
-      </c>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
     </row>
     <row r="29" spans="1:21">
-      <c r="A29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29">
-        <v>5284</v>
-      </c>
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
     </row>
     <row r="30" spans="1:21">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30">
-        <v>4327</v>
-      </c>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
     </row>
     <row r="31" spans="1:21">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31">
-        <v>3874</v>
-      </c>
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
     </row>
     <row r="32" spans="1:21">
-      <c r="A32" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32">
-        <v>3771</v>
-      </c>
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33">
-        <v>4174</v>
-      </c>
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34">
-        <v>4962</v>
-      </c>
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35">
-        <v>1670</v>
-      </c>
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>1</v>
-      </c>
-      <c r="B36">
-        <v>2948</v>
-      </c>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37">
-        <v>4525</v>
-      </c>
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38">
-        <v>896</v>
-      </c>
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39">
-        <v>406</v>
-      </c>
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40">
-        <v>221</v>
-      </c>
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41">
-        <v>787</v>
-      </c>
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>10</v>
-      </c>
-      <c r="B42">
-        <v>738</v>
-      </c>
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43">
-        <v>542</v>
-      </c>
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44">
-        <v>507</v>
-      </c>
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" t="s">
-        <v>20</v>
-      </c>
-      <c r="B45">
-        <v>2</v>
-      </c>
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>22</v>
-      </c>
-      <c r="B46">
-        <v>36</v>
-      </c>
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>3</v>
-      </c>
-      <c r="B47">
-        <v>6</v>
-      </c>
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>4</v>
-      </c>
-      <c r="B48">
-        <v>9</v>
-      </c>
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>24</v>
-      </c>
-      <c r="B49" s="9"/>
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -1,24 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kewart/Documents/GitHub/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CBDBC3-1CFD-AC40-B2BF-3F6AA87D9D6B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B531E389-2237-5D49-870B-34291B061D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9780" yWindow="880" windowWidth="22260" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="820" yWindow="1560" windowWidth="20620" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -253,7 +263,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -328,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -344,8 +354,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,8 +688,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
-  <dimension ref="A1:U51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:U24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.33203125" customWidth="1"/>
@@ -691,7 +699,7 @@
     <col min="6" max="21" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -756,7 +764,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -786,14 +794,22 @@
       <c r="O2" s="2">
         <v>1849</v>
       </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
+      <c r="P2" s="2">
+        <v>1588</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>1575</v>
+      </c>
+      <c r="R2" s="2">
+        <v>1849</v>
+      </c>
+      <c r="S2" s="2">
+        <v>1802</v>
+      </c>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -823,14 +839,22 @@
       <c r="O3" s="2">
         <v>3414</v>
       </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
+      <c r="P3" s="2">
+        <v>2920</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>2845</v>
+      </c>
+      <c r="R3" s="2">
+        <v>3414</v>
+      </c>
+      <c r="S3" s="2">
+        <v>3283</v>
+      </c>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -860,14 +884,22 @@
       <c r="O4" s="2">
         <v>5841</v>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
+      <c r="P4" s="2">
+        <v>4955</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>4900</v>
+      </c>
+      <c r="R4" s="2">
+        <v>5841</v>
+      </c>
+      <c r="S4" s="2">
+        <v>5669</v>
+      </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -897,14 +929,22 @@
       <c r="O5" s="2">
         <v>4865</v>
       </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
+      <c r="P5" s="2">
+        <v>4193</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>4117</v>
+      </c>
+      <c r="R5" s="2">
+        <v>4865</v>
+      </c>
+      <c r="S5" s="2">
+        <v>4680</v>
+      </c>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -934,14 +974,22 @@
       <c r="O6" s="2">
         <v>4378</v>
       </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
+      <c r="P6" s="2">
+        <v>3794</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>3766</v>
+      </c>
+      <c r="R6" s="2">
+        <v>4378</v>
+      </c>
+      <c r="S6" s="2">
+        <v>4261</v>
+      </c>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -971,14 +1019,22 @@
       <c r="O7" s="2">
         <v>4248</v>
       </c>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
+      <c r="P7" s="2">
+        <v>3673</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>3637</v>
+      </c>
+      <c r="R7" s="2">
+        <v>4248</v>
+      </c>
+      <c r="S7" s="2">
+        <v>4132</v>
+      </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1008,14 +1064,22 @@
       <c r="O8" s="2">
         <v>4621</v>
       </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
+      <c r="P8" s="2">
+        <v>4031</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>3926</v>
+      </c>
+      <c r="R8" s="2">
+        <v>4621</v>
+      </c>
+      <c r="S8" s="2">
+        <v>4492</v>
+      </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1045,14 +1109,22 @@
       <c r="O9" s="2">
         <v>5389</v>
       </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
+      <c r="P9" s="2">
+        <v>4619</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>4561</v>
+      </c>
+      <c r="R9" s="2">
+        <v>5389</v>
+      </c>
+      <c r="S9" s="2">
+        <v>5260</v>
+      </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1082,14 +1154,22 @@
       <c r="O10" s="2">
         <v>1814</v>
       </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
+      <c r="P10" s="2">
+        <v>1532</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>1499</v>
+      </c>
+      <c r="R10" s="2">
+        <v>1814</v>
+      </c>
+      <c r="S10" s="2">
+        <v>1741</v>
+      </c>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1119,14 +1199,22 @@
       <c r="O11" s="2">
         <v>3120</v>
       </c>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
+      <c r="P11" s="2">
+        <v>2751</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>2705</v>
+      </c>
+      <c r="R11" s="2">
+        <v>3120</v>
+      </c>
+      <c r="S11" s="2">
+        <v>3056</v>
+      </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1156,14 +1244,22 @@
       <c r="O12" s="2">
         <v>4822</v>
       </c>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
+      <c r="P12" s="2">
+        <v>4257</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>4226</v>
+      </c>
+      <c r="R12" s="2">
+        <v>4822</v>
+      </c>
+      <c r="S12" s="2">
+        <v>4690</v>
+      </c>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
     </row>
-    <row r="13" spans="1:21" ht="17">
+    <row r="13" spans="1:21" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -1193,14 +1289,22 @@
       <c r="O13" s="2">
         <v>875</v>
       </c>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
+      <c r="P13" s="2">
+        <v>511</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>506</v>
+      </c>
+      <c r="R13" s="2">
+        <v>875</v>
+      </c>
+      <c r="S13" s="2">
+        <v>839</v>
+      </c>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
     </row>
-    <row r="14" spans="1:21" ht="17">
+    <row r="14" spans="1:21" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
@@ -1230,14 +1334,22 @@
       <c r="O14" s="2">
         <v>466</v>
       </c>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
+      <c r="P14" s="2">
+        <v>308</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>288</v>
+      </c>
+      <c r="R14" s="2">
+        <v>466</v>
+      </c>
+      <c r="S14" s="2">
+        <v>424</v>
+      </c>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
@@ -1267,14 +1379,22 @@
       <c r="O15" s="2">
         <v>246</v>
       </c>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
+      <c r="P15" s="2">
+        <v>101</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>93</v>
+      </c>
+      <c r="R15" s="2">
+        <v>246</v>
+      </c>
+      <c r="S15" s="2">
+        <v>226</v>
+      </c>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
@@ -1304,14 +1424,22 @@
       <c r="O16" s="2">
         <v>840</v>
       </c>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
+      <c r="P16" s="2">
+        <v>658</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>644</v>
+      </c>
+      <c r="R16" s="2">
+        <v>840</v>
+      </c>
+      <c r="S16" s="2">
+        <v>793</v>
+      </c>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
@@ -1341,14 +1469,22 @@
       <c r="O17" s="2">
         <v>794</v>
       </c>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
+      <c r="P17" s="2">
+        <v>648</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>639</v>
+      </c>
+      <c r="R17" s="2">
+        <v>794</v>
+      </c>
+      <c r="S17" s="2">
+        <v>781</v>
+      </c>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
@@ -1378,14 +1514,22 @@
       <c r="O18" s="2">
         <v>543</v>
       </c>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
+      <c r="P18" s="2">
+        <v>278</v>
+      </c>
+      <c r="Q18" s="2">
+        <v>277</v>
+      </c>
+      <c r="R18" s="2">
+        <v>543</v>
+      </c>
+      <c r="S18" s="2">
+        <v>517</v>
+      </c>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
@@ -1415,14 +1559,22 @@
       <c r="O19" s="2">
         <v>555</v>
       </c>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
+      <c r="P19" s="2">
+        <v>285</v>
+      </c>
+      <c r="Q19" s="2">
+        <v>280</v>
+      </c>
+      <c r="R19" s="2">
+        <v>555</v>
+      </c>
+      <c r="S19" s="2">
+        <v>526</v>
+      </c>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
@@ -1452,14 +1604,22 @@
       <c r="O20" s="2">
         <v>2</v>
       </c>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
+      <c r="P20" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0</v>
+      </c>
+      <c r="R20" s="2">
+        <v>2</v>
+      </c>
+      <c r="S20" s="2">
+        <v>2</v>
+      </c>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
@@ -1489,14 +1649,22 @@
       <c r="O21" s="2">
         <v>50</v>
       </c>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
+      <c r="P21" s="2">
+        <v>14</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>14</v>
+      </c>
+      <c r="R21" s="2">
+        <v>50</v>
+      </c>
+      <c r="S21" s="2">
+        <v>42</v>
+      </c>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1526,14 +1694,22 @@
       <c r="O22" s="2">
         <v>6</v>
       </c>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
+      <c r="P22" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="2">
+        <v>0</v>
+      </c>
+      <c r="R22" s="2">
+        <v>6</v>
+      </c>
+      <c r="S22" s="2">
+        <v>6</v>
+      </c>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
@@ -1563,14 +1739,22 @@
       <c r="O23" s="2">
         <v>9</v>
       </c>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
+      <c r="P23" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="2">
+        <v>0</v>
+      </c>
+      <c r="R23" s="2">
+        <v>9</v>
+      </c>
+      <c r="S23" s="2">
+        <v>9</v>
+      </c>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
@@ -1588,124 +1772,32 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="9">
+      <c r="L24" s="2">
         <v>7</v>
       </c>
       <c r="M24" s="2">
         <v>46</v>
       </c>
-      <c r="N24" s="9">
+      <c r="N24" s="2">
         <v>7</v>
       </c>
       <c r="O24" s="2">
         <v>46</v>
       </c>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
+      <c r="P24" s="2">
+        <v>7</v>
+      </c>
+      <c r="Q24" s="2">
+        <v>7</v>
+      </c>
+      <c r="R24" s="2">
+        <v>46</v>
+      </c>
+      <c r="S24" s="2">
+        <v>46</v>
+      </c>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
-    </row>
-    <row r="27" spans="1:21">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-    </row>
-    <row r="28" spans="1:21">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-    </row>
-    <row r="29" spans="1:21">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-    </row>
-    <row r="30" spans="1:21">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-    </row>
-    <row r="31" spans="1:21">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-    </row>
-    <row r="32" spans="1:21">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="10"/>
-      <c r="B35" s="10"/>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="10"/>
-      <c r="B37" s="10"/>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="10"/>
-      <c r="B39" s="10"/>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="10"/>
-      <c r="B40" s="10"/>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="10"/>
-      <c r="B41" s="10"/>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="10"/>
-      <c r="B42" s="10"/>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="10"/>
-      <c r="B43" s="10"/>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="10"/>
-      <c r="B44" s="10"/>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="10"/>
-      <c r="B45" s="10"/>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="10"/>
-      <c r="B46" s="10"/>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="10"/>
-      <c r="B47" s="10"/>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="10"/>
-      <c r="B48" s="10"/>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="10"/>
-      <c r="B49" s="10"/>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="10"/>
-      <c r="B50" s="10"/>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" s="10"/>
-      <c r="B51" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kewart/Documents/GitHub/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B531E389-2237-5D49-870B-34291B061D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4B21D0-2AA5-E742-9B5A-4C1CF289645A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="820" yWindow="1560" windowWidth="20620" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="24000" yWindow="3520" windowWidth="20620" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
   <si>
     <t xml:space="preserve">Panesthia cribrata </t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>8.v2. HGT insert count</t>
+  </si>
+  <si>
+    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -279,7 +282,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,6 +310,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -338,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -354,6 +363,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -806,8 +817,12 @@
       <c r="S2" s="2">
         <v>1802</v>
       </c>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
+      <c r="T2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
@@ -851,8 +866,12 @@
       <c r="S3" s="2">
         <v>3283</v>
       </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
+      <c r="T3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -896,8 +915,12 @@
       <c r="S4" s="2">
         <v>5669</v>
       </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
+      <c r="T4" s="10">
+        <v>626</v>
+      </c>
+      <c r="U4" s="10">
+        <v>784</v>
+      </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -941,8 +964,12 @@
       <c r="S5" s="2">
         <v>4680</v>
       </c>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
+      <c r="T5" s="10">
+        <v>536</v>
+      </c>
+      <c r="U5" s="10">
+        <v>641</v>
+      </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -986,8 +1013,12 @@
       <c r="S6" s="2">
         <v>4261</v>
       </c>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
+      <c r="T6" s="10">
+        <v>726</v>
+      </c>
+      <c r="U6" s="10">
+        <v>841</v>
+      </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
@@ -1031,8 +1062,12 @@
       <c r="S7" s="2">
         <v>4132</v>
       </c>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
+      <c r="T7" s="10">
+        <v>591</v>
+      </c>
+      <c r="U7" s="10">
+        <v>703</v>
+      </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1076,8 +1111,12 @@
       <c r="S8" s="2">
         <v>4492</v>
       </c>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
+      <c r="T8" s="10">
+        <v>464</v>
+      </c>
+      <c r="U8" s="10">
+        <v>593</v>
+      </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
@@ -1121,8 +1160,12 @@
       <c r="S9" s="2">
         <v>5260</v>
       </c>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
+      <c r="T9" s="10">
+        <v>652</v>
+      </c>
+      <c r="U9" s="10">
+        <v>794</v>
+      </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
@@ -1166,8 +1209,12 @@
       <c r="S10" s="2">
         <v>1741</v>
       </c>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
+      <c r="T10" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U10" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
@@ -1211,8 +1258,12 @@
       <c r="S11" s="2">
         <v>3056</v>
       </c>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
+      <c r="T11" s="10">
+        <v>573</v>
+      </c>
+      <c r="U11" s="10">
+        <v>656</v>
+      </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -1256,8 +1307,12 @@
       <c r="S12" s="2">
         <v>4690</v>
       </c>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
+      <c r="T12" s="10">
+        <v>616</v>
+      </c>
+      <c r="U12" s="10">
+        <v>719</v>
+      </c>
     </row>
     <row r="13" spans="1:21" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
@@ -1301,8 +1356,12 @@
       <c r="S13" s="2">
         <v>839</v>
       </c>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
+      <c r="T13" s="10">
+        <v>19</v>
+      </c>
+      <c r="U13" s="10">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" spans="1:21" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
@@ -1346,8 +1405,12 @@
       <c r="S14" s="2">
         <v>424</v>
       </c>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
+      <c r="T14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U14" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
@@ -1391,8 +1454,12 @@
       <c r="S15" s="2">
         <v>226</v>
       </c>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
+      <c r="T15" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U15" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
@@ -1436,8 +1503,12 @@
       <c r="S16" s="2">
         <v>793</v>
       </c>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
+      <c r="T16" s="10">
+        <v>2</v>
+      </c>
+      <c r="U16" s="10">
+        <v>5</v>
+      </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
@@ -1481,8 +1552,12 @@
       <c r="S17" s="2">
         <v>781</v>
       </c>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
+      <c r="T17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U17" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
@@ -1526,8 +1601,12 @@
       <c r="S18" s="2">
         <v>517</v>
       </c>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
+      <c r="T18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U18" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
@@ -1571,8 +1650,12 @@
       <c r="S19" s="2">
         <v>526</v>
       </c>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
+      <c r="T19" s="10">
+        <v>7</v>
+      </c>
+      <c r="U19" s="10">
+        <v>23</v>
+      </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
@@ -1616,8 +1699,12 @@
       <c r="S20" s="2">
         <v>2</v>
       </c>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
+      <c r="T20" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U20" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
@@ -1661,8 +1748,12 @@
       <c r="S21" s="2">
         <v>42</v>
       </c>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
+      <c r="T21" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U21" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
@@ -1706,8 +1797,12 @@
       <c r="S22" s="2">
         <v>6</v>
       </c>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
+      <c r="T22" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U22" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
@@ -1751,8 +1846,12 @@
       <c r="S23" s="2">
         <v>9</v>
       </c>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
+      <c r="T23" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U23" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
@@ -1796,8 +1895,12 @@
       <c r="S24" s="2">
         <v>46</v>
       </c>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
+      <c r="T24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="U24" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kewart/Documents/GitHub/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4B21D0-2AA5-E742-9B5A-4C1CF289645A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7887604-B8A5-3743-B76F-4F03511CA6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="24000" yWindow="3520" windowWidth="20620" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
@@ -347,7 +347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -364,7 +364,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,10 +914,10 @@
       <c r="S4" s="2">
         <v>5669</v>
       </c>
-      <c r="T4" s="10">
+      <c r="T4" s="2">
         <v>626</v>
       </c>
-      <c r="U4" s="10">
+      <c r="U4" s="2">
         <v>784</v>
       </c>
     </row>
@@ -964,10 +963,10 @@
       <c r="S5" s="2">
         <v>4680</v>
       </c>
-      <c r="T5" s="10">
+      <c r="T5" s="2">
         <v>536</v>
       </c>
-      <c r="U5" s="10">
+      <c r="U5" s="2">
         <v>641</v>
       </c>
     </row>
@@ -1013,10 +1012,10 @@
       <c r="S6" s="2">
         <v>4261</v>
       </c>
-      <c r="T6" s="10">
+      <c r="T6" s="2">
         <v>726</v>
       </c>
-      <c r="U6" s="10">
+      <c r="U6" s="2">
         <v>841</v>
       </c>
     </row>
@@ -1062,10 +1061,10 @@
       <c r="S7" s="2">
         <v>4132</v>
       </c>
-      <c r="T7" s="10">
+      <c r="T7" s="2">
         <v>591</v>
       </c>
-      <c r="U7" s="10">
+      <c r="U7" s="2">
         <v>703</v>
       </c>
     </row>
@@ -1111,10 +1110,10 @@
       <c r="S8" s="2">
         <v>4492</v>
       </c>
-      <c r="T8" s="10">
+      <c r="T8" s="2">
         <v>464</v>
       </c>
-      <c r="U8" s="10">
+      <c r="U8" s="2">
         <v>593</v>
       </c>
     </row>
@@ -1160,10 +1159,10 @@
       <c r="S9" s="2">
         <v>5260</v>
       </c>
-      <c r="T9" s="10">
+      <c r="T9" s="2">
         <v>652</v>
       </c>
-      <c r="U9" s="10">
+      <c r="U9" s="2">
         <v>794</v>
       </c>
     </row>
@@ -1258,10 +1257,10 @@
       <c r="S11" s="2">
         <v>3056</v>
       </c>
-      <c r="T11" s="10">
+      <c r="T11" s="2">
         <v>573</v>
       </c>
-      <c r="U11" s="10">
+      <c r="U11" s="2">
         <v>656</v>
       </c>
     </row>
@@ -1307,10 +1306,10 @@
       <c r="S12" s="2">
         <v>4690</v>
       </c>
-      <c r="T12" s="10">
+      <c r="T12" s="2">
         <v>616</v>
       </c>
-      <c r="U12" s="10">
+      <c r="U12" s="2">
         <v>719</v>
       </c>
     </row>
@@ -1356,10 +1355,10 @@
       <c r="S13" s="2">
         <v>839</v>
       </c>
-      <c r="T13" s="10">
+      <c r="T13" s="2">
         <v>19</v>
       </c>
-      <c r="U13" s="10">
+      <c r="U13" s="2">
         <v>37</v>
       </c>
     </row>
@@ -1503,10 +1502,10 @@
       <c r="S16" s="2">
         <v>793</v>
       </c>
-      <c r="T16" s="10">
+      <c r="T16" s="2">
         <v>2</v>
       </c>
-      <c r="U16" s="10">
+      <c r="U16" s="2">
         <v>5</v>
       </c>
     </row>
@@ -1650,10 +1649,10 @@
       <c r="S19" s="2">
         <v>526</v>
       </c>
-      <c r="T19" s="10">
+      <c r="T19" s="2">
         <v>7</v>
       </c>
-      <c r="U19" s="10">
+      <c r="U19" s="2">
         <v>23</v>
       </c>
     </row>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -1,34 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kewart/Documents/GitHub/HGT_pipeline/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7887604-B8A5-3743-B76F-4F03511CA6BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C9D54E-FD1F-084C-A4BD-30EBD59F8B2A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24000" yWindow="3520" windowWidth="20620" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="8780" yWindow="1600" windowWidth="20620" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -266,7 +256,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -698,8 +688,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
-  <dimension ref="A1:U24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.33203125" customWidth="1"/>
@@ -709,7 +699,7 @@
     <col min="6" max="21" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -774,7 +764,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -823,7 +813,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -872,7 +862,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -921,7 +911,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -970,7 +960,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1019,7 +1009,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1068,7 +1058,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1117,7 +1107,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1166,7 +1156,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1205,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1264,7 +1254,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1313,7 +1303,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" ht="17">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -1362,7 +1352,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="17">
       <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
@@ -1411,7 +1401,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21">
       <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
@@ -1460,7 +1450,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
@@ -1509,7 +1499,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21">
       <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
@@ -1558,7 +1548,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21">
       <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
@@ -1607,7 +1597,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21">
       <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
@@ -1656,7 +1646,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
@@ -1705,7 +1695,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
@@ -1754,7 +1744,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21">
       <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1803,7 +1793,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21">
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
@@ -1852,7 +1842,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
@@ -1901,6 +1891,16 @@
         <v>74</v>
       </c>
     </row>
+    <row r="25" spans="1:21">
+      <c r="P25">
+        <f>MAX(P2:P24)</f>
+        <v>4955</v>
+      </c>
+      <c r="Q25">
+        <f>MAX(Q2:Q24)</f>
+        <v>4900</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C9D54E-FD1F-084C-A4BD-30EBD59F8B2A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E345FE-D926-1542-8E5F-7D9AB52FF6A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8780" yWindow="1600" windowWidth="20620" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
+    <workbookView xWindow="3620" yWindow="760" windowWidth="25740" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="77">
   <si>
     <t xml:space="preserve">Panesthia cribrata </t>
   </si>
@@ -250,6 +250,12 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>7.v1. HGT insert count - audited</t>
+  </si>
+  <si>
+    <t>7.v2. HGT insert count - audited</t>
   </si>
 </sst>
 </file>
@@ -688,7 +694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
@@ -696,10 +702,14 @@
     <col min="3" max="3" width="51.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.83203125" customWidth="1"/>
     <col min="5" max="5" width="41.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="21" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="16" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="29.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:23">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -749,22 +759,28 @@
         <v>68</v>
       </c>
       <c r="Q1" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="R1" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="T1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:23">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -798,22 +814,28 @@
         <v>1588</v>
       </c>
       <c r="Q2" s="2">
+        <v>1588</v>
+      </c>
+      <c r="R2" s="2">
         <v>1575</v>
       </c>
-      <c r="R2" s="2">
+      <c r="S2" s="2">
+        <v>1575</v>
+      </c>
+      <c r="T2" s="2">
         <v>1849</v>
       </c>
-      <c r="S2" s="2">
+      <c r="U2" s="2">
         <v>1802</v>
       </c>
-      <c r="T2" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U2" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
+      <c r="V2" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W2" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -847,22 +869,28 @@
         <v>2920</v>
       </c>
       <c r="Q3" s="2">
+        <v>2920</v>
+      </c>
+      <c r="R3" s="2">
         <v>2845</v>
       </c>
-      <c r="R3" s="2">
+      <c r="S3" s="2">
+        <v>2845</v>
+      </c>
+      <c r="T3" s="2">
         <v>3414</v>
       </c>
-      <c r="S3" s="2">
+      <c r="U3" s="2">
         <v>3283</v>
       </c>
-      <c r="T3" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U3" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
+      <c r="V3" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -896,22 +924,28 @@
         <v>4955</v>
       </c>
       <c r="Q4" s="2">
+        <v>4955</v>
+      </c>
+      <c r="R4" s="2">
         <v>4900</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="2">
+        <v>4900</v>
+      </c>
+      <c r="T4" s="2">
         <v>5841</v>
       </c>
-      <c r="S4" s="2">
+      <c r="U4" s="2">
         <v>5669</v>
       </c>
-      <c r="T4" s="2">
+      <c r="V4" s="2">
         <v>626</v>
       </c>
-      <c r="U4" s="2">
+      <c r="W4" s="2">
         <v>784</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:23">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -945,22 +979,28 @@
         <v>4193</v>
       </c>
       <c r="Q5" s="2">
+        <v>4193</v>
+      </c>
+      <c r="R5" s="2">
         <v>4117</v>
       </c>
-      <c r="R5" s="2">
+      <c r="S5" s="2">
+        <v>4117</v>
+      </c>
+      <c r="T5" s="2">
         <v>4865</v>
       </c>
-      <c r="S5" s="2">
+      <c r="U5" s="2">
         <v>4680</v>
       </c>
-      <c r="T5" s="2">
+      <c r="V5" s="2">
         <v>536</v>
       </c>
-      <c r="U5" s="2">
+      <c r="W5" s="2">
         <v>641</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:23">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -994,22 +1034,28 @@
         <v>3794</v>
       </c>
       <c r="Q6" s="2">
+        <v>3794</v>
+      </c>
+      <c r="R6" s="2">
         <v>3766</v>
       </c>
-      <c r="R6" s="2">
+      <c r="S6" s="2">
+        <v>3766</v>
+      </c>
+      <c r="T6" s="2">
         <v>4378</v>
       </c>
-      <c r="S6" s="2">
+      <c r="U6" s="2">
         <v>4261</v>
       </c>
-      <c r="T6" s="2">
+      <c r="V6" s="2">
         <v>726</v>
       </c>
-      <c r="U6" s="2">
+      <c r="W6" s="2">
         <v>841</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:23">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1043,22 +1089,28 @@
         <v>3673</v>
       </c>
       <c r="Q7" s="2">
+        <v>3673</v>
+      </c>
+      <c r="R7" s="2">
         <v>3637</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
+        <v>3637</v>
+      </c>
+      <c r="T7" s="2">
         <v>4248</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>4132</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>591</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>703</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:23">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1092,22 +1144,28 @@
         <v>4031</v>
       </c>
       <c r="Q8" s="2">
+        <v>4031</v>
+      </c>
+      <c r="R8" s="2">
         <v>3926</v>
       </c>
-      <c r="R8" s="2">
+      <c r="S8" s="2">
+        <v>3926</v>
+      </c>
+      <c r="T8" s="2">
         <v>4621</v>
       </c>
-      <c r="S8" s="2">
+      <c r="U8" s="2">
         <v>4492</v>
       </c>
-      <c r="T8" s="2">
+      <c r="V8" s="2">
         <v>464</v>
       </c>
-      <c r="U8" s="2">
+      <c r="W8" s="2">
         <v>593</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:23">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1141,22 +1199,28 @@
         <v>4619</v>
       </c>
       <c r="Q9" s="2">
+        <v>4619</v>
+      </c>
+      <c r="R9" s="2">
         <v>4561</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
+        <v>4561</v>
+      </c>
+      <c r="T9" s="2">
         <v>5389</v>
       </c>
-      <c r="S9" s="2">
+      <c r="U9" s="2">
         <v>5260</v>
       </c>
-      <c r="T9" s="2">
+      <c r="V9" s="2">
         <v>652</v>
       </c>
-      <c r="U9" s="2">
+      <c r="W9" s="2">
         <v>794</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:23">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,22 +1254,28 @@
         <v>1532</v>
       </c>
       <c r="Q10" s="2">
+        <v>1532</v>
+      </c>
+      <c r="R10" s="2">
         <v>1499</v>
       </c>
-      <c r="R10" s="2">
+      <c r="S10" s="2">
+        <v>1499</v>
+      </c>
+      <c r="T10" s="2">
         <v>1814</v>
       </c>
-      <c r="S10" s="2">
+      <c r="U10" s="2">
         <v>1741</v>
       </c>
-      <c r="T10" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U10" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21">
+      <c r="V10" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W10" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1239,22 +1309,28 @@
         <v>2751</v>
       </c>
       <c r="Q11" s="2">
+        <v>2751</v>
+      </c>
+      <c r="R11" s="2">
         <v>2705</v>
       </c>
-      <c r="R11" s="2">
+      <c r="S11" s="2">
+        <v>2705</v>
+      </c>
+      <c r="T11" s="2">
         <v>3120</v>
       </c>
-      <c r="S11" s="2">
+      <c r="U11" s="2">
         <v>3056</v>
       </c>
-      <c r="T11" s="2">
+      <c r="V11" s="2">
         <v>573</v>
       </c>
-      <c r="U11" s="2">
+      <c r="W11" s="2">
         <v>656</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:23">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1288,22 +1364,28 @@
         <v>4257</v>
       </c>
       <c r="Q12" s="2">
+        <v>4257</v>
+      </c>
+      <c r="R12" s="2">
         <v>4226</v>
       </c>
-      <c r="R12" s="2">
+      <c r="S12" s="2">
+        <v>4226</v>
+      </c>
+      <c r="T12" s="2">
         <v>4822</v>
       </c>
-      <c r="S12" s="2">
+      <c r="U12" s="2">
         <v>4690</v>
       </c>
-      <c r="T12" s="2">
+      <c r="V12" s="2">
         <v>616</v>
       </c>
-      <c r="U12" s="2">
+      <c r="W12" s="2">
         <v>719</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="17">
+    <row r="13" spans="1:23" ht="17">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -1337,22 +1419,28 @@
         <v>511</v>
       </c>
       <c r="Q13" s="2">
+        <v>511</v>
+      </c>
+      <c r="R13" s="2">
         <v>506</v>
       </c>
-      <c r="R13" s="2">
+      <c r="S13" s="2">
+        <v>506</v>
+      </c>
+      <c r="T13" s="2">
         <v>875</v>
       </c>
-      <c r="S13" s="2">
+      <c r="U13" s="2">
         <v>839</v>
       </c>
-      <c r="T13" s="2">
+      <c r="V13" s="2">
         <v>19</v>
       </c>
-      <c r="U13" s="2">
+      <c r="W13" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="17">
+    <row r="14" spans="1:23" ht="17">
       <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
@@ -1386,22 +1474,28 @@
         <v>308</v>
       </c>
       <c r="Q14" s="2">
+        <v>308</v>
+      </c>
+      <c r="R14" s="2">
         <v>288</v>
       </c>
-      <c r="R14" s="2">
+      <c r="S14" s="2">
+        <v>288</v>
+      </c>
+      <c r="T14" s="2">
         <v>466</v>
       </c>
-      <c r="S14" s="2">
+      <c r="U14" s="2">
         <v>424</v>
       </c>
-      <c r="T14" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U14" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21">
+      <c r="V14" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W14" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
@@ -1435,22 +1529,28 @@
         <v>101</v>
       </c>
       <c r="Q15" s="2">
+        <v>101</v>
+      </c>
+      <c r="R15" s="2">
         <v>93</v>
       </c>
-      <c r="R15" s="2">
+      <c r="S15" s="2">
+        <v>93</v>
+      </c>
+      <c r="T15" s="2">
         <v>246</v>
       </c>
-      <c r="S15" s="2">
+      <c r="U15" s="2">
         <v>226</v>
       </c>
-      <c r="T15" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U15" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21">
+      <c r="V15" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W15" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
@@ -1484,22 +1584,28 @@
         <v>658</v>
       </c>
       <c r="Q16" s="2">
+        <v>658</v>
+      </c>
+      <c r="R16" s="2">
         <v>644</v>
       </c>
-      <c r="R16" s="2">
+      <c r="S16" s="2">
+        <v>644</v>
+      </c>
+      <c r="T16" s="2">
         <v>840</v>
       </c>
-      <c r="S16" s="2">
+      <c r="U16" s="2">
         <v>793</v>
       </c>
-      <c r="T16" s="2">
+      <c r="V16" s="2">
         <v>2</v>
       </c>
-      <c r="U16" s="2">
+      <c r="W16" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:23">
       <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
@@ -1533,22 +1639,28 @@
         <v>648</v>
       </c>
       <c r="Q17" s="2">
+        <v>648</v>
+      </c>
+      <c r="R17" s="2">
         <v>639</v>
       </c>
-      <c r="R17" s="2">
+      <c r="S17" s="2">
+        <v>639</v>
+      </c>
+      <c r="T17" s="2">
         <v>794</v>
       </c>
-      <c r="S17" s="2">
+      <c r="U17" s="2">
         <v>781</v>
       </c>
-      <c r="T17" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U17" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21">
+      <c r="V17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W17" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
@@ -1582,22 +1694,28 @@
         <v>278</v>
       </c>
       <c r="Q18" s="2">
+        <v>278</v>
+      </c>
+      <c r="R18" s="2">
         <v>277</v>
       </c>
-      <c r="R18" s="2">
+      <c r="S18" s="2">
+        <v>277</v>
+      </c>
+      <c r="T18" s="2">
         <v>543</v>
       </c>
-      <c r="S18" s="2">
+      <c r="U18" s="2">
         <v>517</v>
       </c>
-      <c r="T18" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U18" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:21">
+      <c r="V18" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W18" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
@@ -1631,22 +1749,28 @@
         <v>285</v>
       </c>
       <c r="Q19" s="2">
+        <v>285</v>
+      </c>
+      <c r="R19" s="2">
         <v>280</v>
       </c>
-      <c r="R19" s="2">
+      <c r="S19" s="2">
+        <v>280</v>
+      </c>
+      <c r="T19" s="2">
         <v>555</v>
       </c>
-      <c r="S19" s="2">
+      <c r="U19" s="2">
         <v>526</v>
       </c>
-      <c r="T19" s="2">
+      <c r="V19" s="2">
         <v>7</v>
       </c>
-      <c r="U19" s="2">
+      <c r="W19" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:23">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
@@ -1683,19 +1807,25 @@
         <v>0</v>
       </c>
       <c r="R20" s="2">
+        <v>0</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0</v>
+      </c>
+      <c r="T20" s="2">
         <v>2</v>
       </c>
-      <c r="S20" s="2">
+      <c r="U20" s="2">
         <v>2</v>
       </c>
-      <c r="T20" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U20" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21">
+      <c r="V20" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W20" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
@@ -1729,22 +1859,28 @@
         <v>14</v>
       </c>
       <c r="Q21" s="2">
+        <v>1</v>
+      </c>
+      <c r="R21" s="2">
         <v>14</v>
       </c>
-      <c r="R21" s="2">
+      <c r="S21" s="2">
+        <v>1</v>
+      </c>
+      <c r="T21" s="2">
         <v>50</v>
       </c>
-      <c r="S21" s="2">
+      <c r="U21" s="2">
         <v>42</v>
       </c>
-      <c r="T21" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U21" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
+      <c r="V21" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W21" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1781,19 +1917,25 @@
         <v>0</v>
       </c>
       <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="2">
+        <v>0</v>
+      </c>
+      <c r="T22" s="2">
         <v>6</v>
       </c>
-      <c r="S22" s="2">
+      <c r="U22" s="2">
         <v>6</v>
       </c>
-      <c r="T22" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U22" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
+      <c r="V22" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W22" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
@@ -1830,19 +1972,25 @@
         <v>0</v>
       </c>
       <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="2">
+        <v>0</v>
+      </c>
+      <c r="T23" s="2">
         <v>9</v>
       </c>
-      <c r="S23" s="2">
+      <c r="U23" s="2">
         <v>9</v>
       </c>
-      <c r="T23" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U23" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21">
+      <c r="V23" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W23" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
@@ -1876,29 +2024,25 @@
         <v>7</v>
       </c>
       <c r="Q24" s="2">
+        <v>0</v>
+      </c>
+      <c r="R24" s="2">
         <v>7</v>
       </c>
-      <c r="R24" s="2">
+      <c r="S24" s="2">
+        <v>0</v>
+      </c>
+      <c r="T24" s="2">
         <v>46</v>
       </c>
-      <c r="S24" s="2">
+      <c r="U24" s="2">
         <v>46</v>
       </c>
-      <c r="T24" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="U24" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21">
-      <c r="P25">
-        <f>MAX(P2:P24)</f>
-        <v>4955</v>
-      </c>
-      <c r="Q25">
-        <f>MAX(Q2:Q24)</f>
-        <v>4900</v>
+      <c r="V24" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="W24" s="9" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/data/HGT-inserts_summary.xlsx
+++ b/data/HGT-inserts_summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kyleewart/Documents/PostDoc/HGT_pipeline/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kewart/Documents/GitHub/HGT_pipeline/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E345FE-D926-1542-8E5F-7D9AB52FF6A7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2A045A-CDA7-F74D-9D7F-5750F082579D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3620" yWindow="760" windowWidth="25740" windowHeight="16380" xr2:uid="{3365DD2C-654A-1041-91AD-AF43EE6D7734}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="78">
   <si>
     <t xml:space="preserve">Panesthia cribrata </t>
   </si>
@@ -256,13 +256,16 @@
   </si>
   <si>
     <t>7.v2. HGT insert count - audited</t>
+  </si>
+  <si>
+    <t>8.v1. HGT insert count - audited</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -694,8 +697,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40A815C-EDAC-574C-BA26-EF35C495DFC6}">
-  <dimension ref="A1:W24"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A1:X24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="46" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.33203125" customWidth="1"/>
@@ -706,10 +709,12 @@
     <col min="17" max="17" width="29.83203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="29.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="23" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27.5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>33</v>
       </c>
@@ -777,10 +782,13 @@
         <v>72</v>
       </c>
       <c r="W1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="X1" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
@@ -834,8 +842,11 @@
       <c r="W2" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="3" spans="1:23">
+      <c r="X2" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -889,8 +900,11 @@
       <c r="W3" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="4" spans="1:23">
+      <c r="X3" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -942,10 +956,13 @@
         <v>626</v>
       </c>
       <c r="W4" s="2">
+        <v>626</v>
+      </c>
+      <c r="X4" s="2">
         <v>784</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -997,10 +1014,13 @@
         <v>536</v>
       </c>
       <c r="W5" s="2">
+        <v>536</v>
+      </c>
+      <c r="X5" s="2">
         <v>641</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -1052,10 +1072,13 @@
         <v>726</v>
       </c>
       <c r="W6" s="2">
+        <v>726</v>
+      </c>
+      <c r="X6" s="2">
         <v>841</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -1107,10 +1130,13 @@
         <v>591</v>
       </c>
       <c r="W7" s="2">
+        <v>591</v>
+      </c>
+      <c r="X7" s="2">
         <v>703</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1162,10 +1188,13 @@
         <v>464</v>
       </c>
       <c r="W8" s="2">
+        <v>464</v>
+      </c>
+      <c r="X8" s="2">
         <v>593</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
@@ -1217,10 +1246,13 @@
         <v>652</v>
       </c>
       <c r="W9" s="2">
+        <v>652</v>
+      </c>
+      <c r="X9" s="2">
         <v>794</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>0</v>
       </c>
@@ -1274,8 +1306,11 @@
       <c r="W10" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" spans="1:23">
+      <c r="X10" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1327,10 +1362,13 @@
         <v>573</v>
       </c>
       <c r="W11" s="2">
+        <v>573</v>
+      </c>
+      <c r="X11" s="2">
         <v>656</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>18</v>
       </c>
@@ -1382,10 +1420,13 @@
         <v>616</v>
       </c>
       <c r="W12" s="2">
+        <v>616</v>
+      </c>
+      <c r="X12" s="2">
         <v>719</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="17">
+    <row r="13" spans="1:24" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
@@ -1437,10 +1478,13 @@
         <v>19</v>
       </c>
       <c r="W13" s="2">
+        <v>19</v>
+      </c>
+      <c r="X13" s="2">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="17">
+    <row r="14" spans="1:24" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
         <v>11</v>
       </c>
@@ -1494,8 +1538,11 @@
       <c r="W14" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="15" spans="1:23">
+      <c r="X14" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
         <v>7</v>
       </c>
@@ -1549,8 +1596,11 @@
       <c r="W15" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="16" spans="1:23">
+      <c r="X15" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
@@ -1602,10 +1652,13 @@
         <v>2</v>
       </c>
       <c r="W16" s="2">
+        <v>0</v>
+      </c>
+      <c r="X16" s="2">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A17" s="6" t="s">
         <v>10</v>
       </c>
@@ -1659,8 +1712,11 @@
       <c r="W17" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="X17" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
         <v>17</v>
       </c>
@@ -1714,8 +1770,11 @@
       <c r="W18" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="X18" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A19" s="6" t="s">
         <v>8</v>
       </c>
@@ -1767,10 +1826,13 @@
         <v>7</v>
       </c>
       <c r="W19" s="2">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2">
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
@@ -1824,8 +1886,11 @@
       <c r="W20" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="X20" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
@@ -1879,8 +1944,11 @@
       <c r="W21" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="X21" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1934,8 +2002,11 @@
       <c r="W22" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="X22" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>4</v>
       </c>
@@ -1989,8 +2060,11 @@
       <c r="W23" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="X23" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
         <v>24</v>
       </c>
@@ -2044,6 +2118,9 @@
       <c r="W24" s="9" t="s">
         <v>74</v>
       </c>
+      <c r="X24" s="9" t="s">
+        <v>74</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
